--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/101.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/101.xlsx
@@ -426,13 +426,13 @@
         <v>-12.4466548922076</v>
       </c>
       <c r="E2">
-        <v>-12.45047530154629</v>
+        <v>-10.82181868163566</v>
       </c>
       <c r="F2">
-        <v>-2.004955757961347</v>
+        <v>-1.980639032852168</v>
       </c>
       <c r="G2">
-        <v>-9.209352874360325</v>
+        <v>-8.32179892582726</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.22123428153282</v>
       </c>
       <c r="E3">
-        <v>-13.23916339167017</v>
+        <v>-11.60153586475035</v>
       </c>
       <c r="F3">
-        <v>-1.771758736929647</v>
+        <v>-2.352442629557295</v>
       </c>
       <c r="G3">
-        <v>-9.169334999881615</v>
+        <v>-8.060123474766646</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.05394367188504</v>
       </c>
       <c r="E4">
-        <v>-13.45408476807421</v>
+        <v>-12.31200362333975</v>
       </c>
       <c r="F4">
-        <v>-1.563674502081217</v>
+        <v>-2.097179557649822</v>
       </c>
       <c r="G4">
-        <v>-8.618019919590166</v>
+        <v>-8.015649605992078</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.97679961276661</v>
       </c>
       <c r="E5">
-        <v>-13.67473013562394</v>
+        <v>-13.46356739264627</v>
       </c>
       <c r="F5">
-        <v>-1.3833198660415</v>
+        <v>-2.210364366098735</v>
       </c>
       <c r="G5">
-        <v>-8.747823099639451</v>
+        <v>-8.735259579317916</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.97347354627215</v>
       </c>
       <c r="E6">
-        <v>-14.59934490156206</v>
+        <v>-13.20302616908897</v>
       </c>
       <c r="F6">
-        <v>-1.248306748161417</v>
+        <v>-1.803825667459419</v>
       </c>
       <c r="G6">
-        <v>-8.775979289450952</v>
+        <v>-7.637730969411036</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.03823766188108</v>
       </c>
       <c r="E7">
-        <v>-15.6094029150769</v>
+        <v>-13.47523274169003</v>
       </c>
       <c r="F7">
-        <v>-1.012380256537493</v>
+        <v>-1.987482175966694</v>
       </c>
       <c r="G7">
-        <v>-8.489348946115314</v>
+        <v>-7.68368134149612</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.1555680788555</v>
       </c>
       <c r="E8">
-        <v>-15.84126531274363</v>
+        <v>-14.22530653395051</v>
       </c>
       <c r="F8">
-        <v>-1.208415059144801</v>
+        <v>-1.796744782900289</v>
       </c>
       <c r="G8">
-        <v>-8.304948249032369</v>
+        <v>-7.976995676275547</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.30207421197452</v>
       </c>
       <c r="E9">
-        <v>-16.86979497173576</v>
+        <v>-15.33483247904383</v>
       </c>
       <c r="F9">
-        <v>-1.224601358195504</v>
+        <v>-1.387252954469992</v>
       </c>
       <c r="G9">
-        <v>-8.141642348125661</v>
+        <v>-7.57385068268526</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.45893667657831</v>
       </c>
       <c r="E10">
-        <v>-17.12567639553918</v>
+        <v>-17.05975992788353</v>
       </c>
       <c r="F10">
-        <v>-0.9483789342623974</v>
+        <v>-1.48992578057738</v>
       </c>
       <c r="G10">
-        <v>-7.917094665287975</v>
+        <v>-7.28490626801767</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.59699052327761</v>
       </c>
       <c r="E11">
-        <v>-18.26438382713793</v>
+        <v>-15.81583340271655</v>
       </c>
       <c r="F11">
-        <v>-0.5392035421799704</v>
+        <v>-1.133827201461928</v>
       </c>
       <c r="G11">
-        <v>-7.672468523754609</v>
+        <v>-7.025554819925626</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.69827589697451</v>
       </c>
       <c r="E12">
-        <v>-18.71386204324325</v>
+        <v>-16.93245093810589</v>
       </c>
       <c r="F12">
-        <v>-0.2809293547633209</v>
+        <v>-0.7863171355787021</v>
       </c>
       <c r="G12">
-        <v>-8.00719116213924</v>
+        <v>-6.034632397474357</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.73960672038226</v>
       </c>
       <c r="E13">
-        <v>-19.95293857274801</v>
+        <v>-17.18132681261944</v>
       </c>
       <c r="F13">
-        <v>-0.0959400031049409</v>
+        <v>-1.023056255624773</v>
       </c>
       <c r="G13">
-        <v>-6.855227251930123</v>
+        <v>-5.839707476122069</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.71853290504784</v>
       </c>
       <c r="E14">
-        <v>-20.64820877256766</v>
+        <v>-18.33602881441328</v>
       </c>
       <c r="F14">
-        <v>-0.2487091762640313</v>
+        <v>-0.5480364237960215</v>
       </c>
       <c r="G14">
-        <v>-7.219029722331713</v>
+        <v>-5.889342485392362</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.63946009213363</v>
       </c>
       <c r="E15">
-        <v>-21.29841159906298</v>
+        <v>-19.38164893431036</v>
       </c>
       <c r="F15">
-        <v>0.3004735607699569</v>
+        <v>-0.5174671815305113</v>
       </c>
       <c r="G15">
-        <v>-6.243958191922474</v>
+        <v>-6.122332059355189</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.51490084543755</v>
       </c>
       <c r="E16">
-        <v>-21.54342468524798</v>
+        <v>-19.52516080408744</v>
       </c>
       <c r="F16">
-        <v>0.3933144941735171</v>
+        <v>0.1153384164486842</v>
       </c>
       <c r="G16">
-        <v>-6.904961577566595</v>
+        <v>-5.468323856435549</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.37351638525259</v>
       </c>
       <c r="E17">
-        <v>-23.28713171579749</v>
+        <v>-21.40986640133976</v>
       </c>
       <c r="F17">
-        <v>0.9555605851496536</v>
+        <v>0.2688522919028914</v>
       </c>
       <c r="G17">
-        <v>-6.926576129392496</v>
+        <v>-5.701690832589853</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.2347331790142</v>
       </c>
       <c r="E18">
-        <v>-23.90004255883964</v>
+        <v>-21.91758079318373</v>
       </c>
       <c r="F18">
-        <v>0.9787681263064845</v>
+        <v>0.6185301952792439</v>
       </c>
       <c r="G18">
-        <v>-6.720100714653691</v>
+        <v>-5.616778650053087</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.12428178963824</v>
       </c>
       <c r="E19">
-        <v>-24.56148505782199</v>
+        <v>-22.34004666183331</v>
       </c>
       <c r="F19">
-        <v>1.587088012226329</v>
+        <v>1.066573414268426</v>
       </c>
       <c r="G19">
-        <v>-6.93696131074919</v>
+        <v>-5.438085333479846</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.05065298025655</v>
       </c>
       <c r="E20">
-        <v>-24.77264780079966</v>
+        <v>-23.46145079424875</v>
       </c>
       <c r="F20">
-        <v>1.915775913983145</v>
+        <v>1.441169437488391</v>
       </c>
       <c r="G20">
-        <v>-6.501958937434495</v>
+        <v>-5.762432722144401</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.02558299666079</v>
       </c>
       <c r="E21">
-        <v>-25.41607603017951</v>
+        <v>-23.47605059444948</v>
       </c>
       <c r="F21">
-        <v>2.218522662153892</v>
+        <v>1.642368282484752</v>
       </c>
       <c r="G21">
-        <v>-6.114807189344426</v>
+        <v>-5.773943488984447</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.04729549674334</v>
       </c>
       <c r="E22">
-        <v>-25.62183177519202</v>
+        <v>-24.66412744967985</v>
       </c>
       <c r="F22">
-        <v>2.742425282789245</v>
+        <v>1.662601984665532</v>
       </c>
       <c r="G22">
-        <v>-6.326215316936745</v>
+        <v>-5.785292039093068</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.11084109319281</v>
       </c>
       <c r="E23">
-        <v>-26.73508465439365</v>
+        <v>-23.60318297374082</v>
       </c>
       <c r="F23">
-        <v>2.880842162327431</v>
+        <v>1.981651003323373</v>
       </c>
       <c r="G23">
-        <v>-7.15976102554214</v>
+        <v>-6.204152192358277</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-12.20899731801361</v>
       </c>
       <c r="E24">
-        <v>-26.64481405352475</v>
+        <v>-24.77353538170517</v>
       </c>
       <c r="F24">
-        <v>2.874266581884009</v>
+        <v>2.28656973082426</v>
       </c>
       <c r="G24">
-        <v>-6.736762690352843</v>
+        <v>-6.178833140073931</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.3221475226547</v>
       </c>
       <c r="E25">
-        <v>-27.01176083084029</v>
+        <v>-25.33128488285989</v>
       </c>
       <c r="F25">
-        <v>2.972136533789965</v>
+        <v>2.517985761939941</v>
       </c>
       <c r="G25">
-        <v>-6.92437792715442</v>
+        <v>-5.510645870609592</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.43838975514191</v>
       </c>
       <c r="E26">
-        <v>-27.66884693782727</v>
+        <v>-24.48722261257021</v>
       </c>
       <c r="F26">
-        <v>3.13899789320548</v>
+        <v>2.375781586636156</v>
       </c>
       <c r="G26">
-        <v>-7.84452750706715</v>
+        <v>-6.389572537467317</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.53681663257661</v>
       </c>
       <c r="E27">
-        <v>-28.06037427205644</v>
+        <v>-24.29628403451079</v>
       </c>
       <c r="F27">
-        <v>2.998859666204277</v>
+        <v>2.762977078052701</v>
       </c>
       <c r="G27">
-        <v>-7.068942829763314</v>
+        <v>-6.216149609392596</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.60950484574477</v>
       </c>
       <c r="E28">
-        <v>-26.7579579766064</v>
+        <v>-23.99905311454334</v>
       </c>
       <c r="F28">
-        <v>3.26934978771001</v>
+        <v>2.434872346947456</v>
       </c>
       <c r="G28">
-        <v>-7.540745227292548</v>
+        <v>-6.544194877424517</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.64118394765961</v>
       </c>
       <c r="E29">
-        <v>-26.26033302485152</v>
+        <v>-24.86384673884014</v>
       </c>
       <c r="F29">
-        <v>3.127674110809211</v>
+        <v>2.886907468450729</v>
       </c>
       <c r="G29">
-        <v>-7.149948568563741</v>
+        <v>-6.058746411182407</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.62861432271994</v>
       </c>
       <c r="E30">
-        <v>-26.42112555144186</v>
+        <v>-24.58885062625035</v>
       </c>
       <c r="F30">
-        <v>3.265014112723758</v>
+        <v>2.56352111807183</v>
       </c>
       <c r="G30">
-        <v>-7.473878828490348</v>
+        <v>-6.331929318537527</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.5684087829141</v>
       </c>
       <c r="E31">
-        <v>-26.62895080907588</v>
+        <v>-24.20565568419529</v>
       </c>
       <c r="F31">
-        <v>3.027708389374172</v>
+        <v>2.645615641158872</v>
       </c>
       <c r="G31">
-        <v>-7.08971981356778</v>
+        <v>-6.45519748169229</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.45722510086235</v>
       </c>
       <c r="E32">
-        <v>-25.89033858452882</v>
+        <v>-23.93953990913454</v>
       </c>
       <c r="F32">
-        <v>2.874983948054833</v>
+        <v>2.340826138972822</v>
       </c>
       <c r="G32">
-        <v>-6.412501375872309</v>
+        <v>-5.96307495564301</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.30374042873403</v>
       </c>
       <c r="E33">
-        <v>-24.9605296589039</v>
+        <v>-23.38775440824792</v>
       </c>
       <c r="F33">
-        <v>2.439656997066026</v>
+        <v>2.18740255556552</v>
       </c>
       <c r="G33">
-        <v>-6.594915745631691</v>
+        <v>-5.659276123140711</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.11072709146822</v>
       </c>
       <c r="E34">
-        <v>-25.20929685004126</v>
+        <v>-23.46470223858626</v>
       </c>
       <c r="F34">
-        <v>2.814050898639707</v>
+        <v>2.222732425294919</v>
       </c>
       <c r="G34">
-        <v>-6.679490252523451</v>
+        <v>-5.534074601391014</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.89227355182841</v>
       </c>
       <c r="E35">
-        <v>-24.7965219157681</v>
+        <v>-22.34044516754598</v>
       </c>
       <c r="F35">
-        <v>2.810855057199706</v>
+        <v>2.324671317883426</v>
       </c>
       <c r="G35">
-        <v>-7.588933528162179</v>
+        <v>-5.576509174113392</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.65296894421521</v>
       </c>
       <c r="E36">
-        <v>-24.27537154154338</v>
+        <v>-21.30768591383069</v>
       </c>
       <c r="F36">
-        <v>2.691207326274151</v>
+        <v>1.951798298861285</v>
       </c>
       <c r="G36">
-        <v>-6.476298898959604</v>
+        <v>-5.684949403797759</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.40746525762867</v>
       </c>
       <c r="E37">
-        <v>-23.69284223061868</v>
+        <v>-21.12470839307676</v>
       </c>
       <c r="F37">
-        <v>2.569942622178332</v>
+        <v>1.953673722661223</v>
       </c>
       <c r="G37">
-        <v>-5.834334460711831</v>
+        <v>-4.957235214991784</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.1604351526349</v>
       </c>
       <c r="E38">
-        <v>-23.4158400040435</v>
+        <v>-21.37472997151425</v>
       </c>
       <c r="F38">
-        <v>2.631463812449445</v>
+        <v>1.732988362881406</v>
       </c>
       <c r="G38">
-        <v>-5.83202369992542</v>
+        <v>-5.283506030614656</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.91760997667935</v>
       </c>
       <c r="E39">
-        <v>-22.99036270017882</v>
+        <v>-21.23341894010489</v>
       </c>
       <c r="F39">
-        <v>2.366664575000944</v>
+        <v>1.628668742377253</v>
       </c>
       <c r="G39">
-        <v>-5.355401148091008</v>
+        <v>-4.651221627523713</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.68476714044496</v>
       </c>
       <c r="E40">
-        <v>-22.54709755041201</v>
+        <v>-20.61283233361974</v>
       </c>
       <c r="F40">
-        <v>2.596510021520917</v>
+        <v>1.38099848608384</v>
       </c>
       <c r="G40">
-        <v>-5.434966799581852</v>
+        <v>-4.477153143068834</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.45967300254497</v>
       </c>
       <c r="E41">
-        <v>-21.88689132483375</v>
+        <v>-19.29182212389421</v>
       </c>
       <c r="F41">
-        <v>2.373775280786575</v>
+        <v>1.621052732475915</v>
       </c>
       <c r="G41">
-        <v>-5.572126011819397</v>
+        <v>-4.209346561669491</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.24603133737901</v>
       </c>
       <c r="E42">
-        <v>-21.19497219577977</v>
+        <v>-20.21153255248202</v>
       </c>
       <c r="F42">
-        <v>2.015973578290968</v>
+        <v>1.528394868268373</v>
       </c>
       <c r="G42">
-        <v>-5.082870418207126</v>
+        <v>-4.425247099558601</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.03893952709925</v>
       </c>
       <c r="E43">
-        <v>-21.24324120022753</v>
+        <v>-19.34864541574245</v>
       </c>
       <c r="F43">
-        <v>2.222712544477252</v>
+        <v>1.452160216188735</v>
       </c>
       <c r="G43">
-        <v>-5.33041315036059</v>
+        <v>-4.10715002087219</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.844366948761882</v>
       </c>
       <c r="E44">
-        <v>-20.08687271999887</v>
+        <v>-18.82603234441325</v>
       </c>
       <c r="F44">
-        <v>1.702603846546721</v>
+        <v>1.313522990921404</v>
       </c>
       <c r="G44">
-        <v>-5.009071737045693</v>
+        <v>-3.826644186784203</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.658328026133018</v>
       </c>
       <c r="E45">
-        <v>-19.92988411157496</v>
+        <v>-18.12564496896493</v>
       </c>
       <c r="F45">
-        <v>1.857800136196013</v>
+        <v>0.9912880712323963</v>
       </c>
       <c r="G45">
-        <v>-4.909904345416824</v>
+        <v>-3.821618778655589</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.485737858561574</v>
       </c>
       <c r="E46">
-        <v>-20.05833880527654</v>
+        <v>-16.72206709265754</v>
       </c>
       <c r="F46">
-        <v>1.499430173662086</v>
+        <v>0.9425916650914244</v>
       </c>
       <c r="G46">
-        <v>-4.943175328086499</v>
+        <v>-3.237045957876622</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.32728449837445</v>
       </c>
       <c r="E47">
-        <v>-18.92204957879789</v>
+        <v>-16.89501404348448</v>
       </c>
       <c r="F47">
-        <v>1.587682780021539</v>
+        <v>0.6320052478205834</v>
       </c>
       <c r="G47">
-        <v>-4.608144808966716</v>
+        <v>-3.224992261568135</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.181266382524626</v>
       </c>
       <c r="E48">
-        <v>-19.18720531736901</v>
+        <v>-16.82325584435893</v>
       </c>
       <c r="F48">
-        <v>1.258191361884008</v>
+        <v>1.057161503837819</v>
       </c>
       <c r="G48">
-        <v>-3.927228491903879</v>
+        <v>-2.474130738351577</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.049710652371976</v>
       </c>
       <c r="E49">
-        <v>-18.02358675025406</v>
+        <v>-16.25016387326623</v>
       </c>
       <c r="F49">
-        <v>1.155212039837585</v>
+        <v>0.6210177825898509</v>
       </c>
       <c r="G49">
-        <v>-5.042438725536007</v>
+        <v>-3.16033730718617</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.926506204136258</v>
       </c>
       <c r="E50">
-        <v>-18.18570611972866</v>
+        <v>-15.95134345892208</v>
       </c>
       <c r="F50">
-        <v>0.9173844450242356</v>
+        <v>0.4698059401480235</v>
       </c>
       <c r="G50">
-        <v>-4.966302799223848</v>
+        <v>-3.545340511221251</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.812478951457496</v>
       </c>
       <c r="E51">
-        <v>-17.66909327645962</v>
+        <v>-15.50273018135222</v>
       </c>
       <c r="F51">
-        <v>0.9522338616600108</v>
+        <v>0.4425592795351421</v>
       </c>
       <c r="G51">
-        <v>-4.773930308482338</v>
+        <v>-3.223959371359883</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.696808497262666</v>
       </c>
       <c r="E52">
-        <v>-17.03037466004775</v>
+        <v>-15.106452477889</v>
       </c>
       <c r="F52">
-        <v>0.9383454537846743</v>
+        <v>0.0119730751925563</v>
       </c>
       <c r="G52">
-        <v>-4.992082017338153</v>
+        <v>-2.704670508615344</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.578971067833699</v>
       </c>
       <c r="E53">
-        <v>-16.19536480929941</v>
+        <v>-14.9564331909629</v>
       </c>
       <c r="F53">
-        <v>0.6355548021415793</v>
+        <v>0.1861721130620699</v>
       </c>
       <c r="G53">
-        <v>-4.836800878818638</v>
+        <v>-3.406585616033778</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.451926958504519</v>
       </c>
       <c r="E54">
-        <v>-16.52368370332952</v>
+        <v>-14.89542106065756</v>
       </c>
       <c r="F54">
-        <v>0.6233231290718418</v>
+        <v>0.1492733154717688</v>
       </c>
       <c r="G54">
-        <v>-4.849695453694099</v>
+        <v>-3.599573868245592</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.312171963202106</v>
       </c>
       <c r="E55">
-        <v>-16.32697584938433</v>
+        <v>-14.36998222154756</v>
       </c>
       <c r="F55">
-        <v>0.7412039523272255</v>
+        <v>0.5103106210427109</v>
       </c>
       <c r="G55">
-        <v>-4.977035587862165</v>
+        <v>-3.587940611220593</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.158105637696167</v>
       </c>
       <c r="E56">
-        <v>-15.09566565280273</v>
+        <v>-14.26199170188665</v>
       </c>
       <c r="F56">
-        <v>0.403904343050906</v>
+        <v>0.211155673930503</v>
       </c>
       <c r="G56">
-        <v>-5.256972008117398</v>
+        <v>-3.339020692122793</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.986563850565939</v>
       </c>
       <c r="E57">
-        <v>-14.93243227872225</v>
+        <v>-13.92441207851085</v>
       </c>
       <c r="F57">
-        <v>0.4496691569533703</v>
+        <v>0.1417028657775841</v>
       </c>
       <c r="G57">
-        <v>-4.947790228568244</v>
+        <v>-3.520296234216665</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.801193279680594</v>
       </c>
       <c r="E58">
-        <v>-15.60860590365155</v>
+        <v>-12.45846805816983</v>
       </c>
       <c r="F58">
-        <v>1.017472764834889</v>
+        <v>-0.1337806544322251</v>
       </c>
       <c r="G58">
-        <v>-5.433030130441378</v>
+        <v>-4.048262036819634</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.599056026770954</v>
       </c>
       <c r="E59">
-        <v>-14.65962794755217</v>
+        <v>-12.78511594529111</v>
       </c>
       <c r="F59">
-        <v>0.5099751322445771</v>
+        <v>0.1937359358170322</v>
       </c>
       <c r="G59">
-        <v>-5.244835548170429</v>
+        <v>-3.809283685976264</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.387095507960466</v>
       </c>
       <c r="E60">
-        <v>-14.40178116602942</v>
+        <v>-12.69048442395282</v>
       </c>
       <c r="F60">
-        <v>0.4990903845717916</v>
+        <v>0.1036418687211552</v>
       </c>
       <c r="G60">
-        <v>-5.411938644810681</v>
+        <v>-3.279222308046937</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.163479549613241</v>
       </c>
       <c r="E61">
-        <v>-14.46661532839724</v>
+        <v>-12.61768467580551</v>
       </c>
       <c r="F61">
-        <v>0.3328826070370848</v>
+        <v>-0.0325872925062375</v>
       </c>
       <c r="G61">
-        <v>-5.548253667935712</v>
+        <v>-3.799981053010912</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.932422007314075</v>
       </c>
       <c r="E62">
-        <v>-14.23771908120553</v>
+        <v>-12.59074478393388</v>
       </c>
       <c r="F62">
-        <v>0.3084002084473454</v>
+        <v>0.1210549798954036</v>
       </c>
       <c r="G62">
-        <v>-5.857253367480206</v>
+        <v>-3.895771688189724</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.694284265726704</v>
       </c>
       <c r="E63">
-        <v>-13.49966385896141</v>
+        <v>-12.82891534589329</v>
       </c>
       <c r="F63">
-        <v>0.1649253175476654</v>
+        <v>-0.02041112005248757</v>
       </c>
       <c r="G63">
-        <v>-5.321242939216808</v>
+        <v>-3.577379970950318</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.449063956022118</v>
       </c>
       <c r="E64">
-        <v>-12.60745938149619</v>
+        <v>-12.49105948560303</v>
       </c>
       <c r="F64">
-        <v>0.09035899741726512</v>
+        <v>-0.02264439857043504</v>
       </c>
       <c r="G64">
-        <v>-5.581084348048664</v>
+        <v>-4.175181731704212</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.198821015574308</v>
       </c>
       <c r="E65">
-        <v>-13.32952003354522</v>
+        <v>-12.60265014210005</v>
       </c>
       <c r="F65">
-        <v>-0.2678800830670203</v>
+        <v>-0.01389601042946946</v>
       </c>
       <c r="G65">
-        <v>-5.70497820431035</v>
+        <v>-3.715916370132199</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.940394274767359</v>
       </c>
       <c r="E66">
-        <v>-13.47785925661448</v>
+        <v>-12.06143409954733</v>
       </c>
       <c r="F66">
-        <v>0.03332921520413035</v>
+        <v>-0.3701644048624949</v>
       </c>
       <c r="G66">
-        <v>-5.233937232255149</v>
+        <v>-3.442081285305844</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.677684551159691</v>
       </c>
       <c r="E67">
-        <v>-13.00259590950948</v>
+        <v>-12.51796767815661</v>
       </c>
       <c r="F67">
-        <v>-0.02550640794710733</v>
+        <v>-0.2852327234208643</v>
       </c>
       <c r="G67">
-        <v>-5.309129653088615</v>
+        <v>-3.324967426308586</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.405975626199371</v>
       </c>
       <c r="E68">
-        <v>-12.75206261350912</v>
+        <v>-12.06438666460033</v>
       </c>
       <c r="F68">
-        <v>-0.2943513917908813</v>
+        <v>-0.6141492545808528</v>
       </c>
       <c r="G68">
-        <v>-4.915548825561282</v>
+        <v>-3.196693718298445</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.130990845567263</v>
       </c>
       <c r="E69">
-        <v>-12.85682885967658</v>
+        <v>-12.53347317315887</v>
       </c>
       <c r="F69">
-        <v>-0.1959728222996064</v>
+        <v>-0.4840243327446897</v>
       </c>
       <c r="G69">
-        <v>-4.756351311668809</v>
+        <v>-3.371517007136279</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.852794288130116</v>
       </c>
       <c r="E70">
-        <v>-13.48609655083443</v>
+        <v>-11.90288316759078</v>
       </c>
       <c r="F70">
-        <v>-0.2257145255297199</v>
+        <v>-0.4096535073213501</v>
       </c>
       <c r="G70">
-        <v>-4.909517011588729</v>
+        <v>-3.183554163053078</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.575763369517386</v>
       </c>
       <c r="E71">
-        <v>-13.28860527088592</v>
+        <v>-12.80980065710692</v>
       </c>
       <c r="F71">
-        <v>-0.1865402026839284</v>
+        <v>-0.5291040868050387</v>
       </c>
       <c r="G71">
-        <v>-4.241435679581647</v>
+        <v>-3.183607131781707</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.303951785452807</v>
       </c>
       <c r="E72">
-        <v>-13.38253487875302</v>
+        <v>-12.63113424360829</v>
       </c>
       <c r="F72">
-        <v>-0.3236615156041362</v>
+        <v>-0.4195632665610405</v>
       </c>
       <c r="G72">
-        <v>-4.485700971651232</v>
+        <v>-3.313483143832855</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.03955762317017</v>
       </c>
       <c r="E73">
-        <v>-13.38299225462779</v>
+        <v>-12.880698446171</v>
       </c>
       <c r="F73">
-        <v>-0.3070146442774773</v>
+        <v>-0.7027340362688291</v>
       </c>
       <c r="G73">
-        <v>-3.631957624710743</v>
+        <v>-2.959350776951476</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.788895259742888</v>
       </c>
       <c r="E74">
-        <v>-14.46087322335551</v>
+        <v>-13.22321410621516</v>
       </c>
       <c r="F74">
-        <v>-0.3198071220789101</v>
+        <v>-0.9195517486449746</v>
       </c>
       <c r="G74">
-        <v>-3.370911177302592</v>
+        <v>-3.346999106872436</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.551377742677742</v>
       </c>
       <c r="E75">
-        <v>-13.78073265519549</v>
+        <v>-12.57000437297875</v>
       </c>
       <c r="F75">
-        <v>-0.6520122718280126</v>
+        <v>-1.077327574386585</v>
       </c>
       <c r="G75">
-        <v>-3.309659463734996</v>
+        <v>-2.604533127143469</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.334421983706538</v>
       </c>
       <c r="E76">
-        <v>-14.20675337594109</v>
+        <v>-13.61323798707379</v>
       </c>
       <c r="F76">
-        <v>-0.8732617498091354</v>
+        <v>-1.030069214056873</v>
       </c>
       <c r="G76">
-        <v>-3.326579661986211</v>
+        <v>-3.232109934477569</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.138366681625644</v>
       </c>
       <c r="E77">
-        <v>-14.11607521241149</v>
+        <v>-13.22626629769633</v>
       </c>
       <c r="F77">
-        <v>-0.6983925627107569</v>
+        <v>-1.185134621656524</v>
       </c>
       <c r="G77">
-        <v>-2.814772632160425</v>
+        <v>-2.385447844445581</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.967165000398956</v>
       </c>
       <c r="E78">
-        <v>-14.77498629442356</v>
+        <v>-14.38461372106635</v>
       </c>
       <c r="F78">
-        <v>-1.045220882221479</v>
+        <v>-1.064836622319771</v>
       </c>
       <c r="G78">
-        <v>-2.459289562699024</v>
+        <v>-1.89178591472054</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.823870519285703</v>
       </c>
       <c r="E79">
-        <v>-15.46761186542274</v>
+        <v>-14.21163507092135</v>
       </c>
       <c r="F79">
-        <v>-0.8663639344460239</v>
+        <v>-1.248543661238618</v>
       </c>
       <c r="G79">
-        <v>-2.287280237569572</v>
+        <v>-1.201384884687691</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.709918636369764</v>
       </c>
       <c r="E80">
-        <v>-15.51909608641594</v>
+        <v>-15.27056890440098</v>
       </c>
       <c r="F80">
-        <v>-1.063500465699056</v>
+        <v>-1.45005065890882</v>
       </c>
       <c r="G80">
-        <v>-2.327701998604073</v>
+        <v>-1.468142023151084</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.630072167430159</v>
       </c>
       <c r="E81">
-        <v>-16.24132429200326</v>
+        <v>-15.75933616099686</v>
       </c>
       <c r="F81">
-        <v>-1.215459495538208</v>
+        <v>-1.512912976005066</v>
       </c>
       <c r="G81">
-        <v>-1.759847432798426</v>
+        <v>-0.983935011486202</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.585366089269797</v>
       </c>
       <c r="E82">
-        <v>-16.95579069314142</v>
+        <v>-16.34164357669518</v>
       </c>
       <c r="F82">
-        <v>-1.304019426204101</v>
+        <v>-1.815878413170152</v>
       </c>
       <c r="G82">
-        <v>-1.618871161554101</v>
+        <v>-1.010975547450969</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.580932509846779</v>
       </c>
       <c r="E83">
-        <v>-17.34778446019338</v>
+        <v>-16.65666234256476</v>
       </c>
       <c r="F83">
-        <v>-1.327178093684166</v>
+        <v>-1.818064474746139</v>
       </c>
       <c r="G83">
-        <v>-0.9252324179838453</v>
+        <v>-0.3277948172392705</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.620122432952119</v>
       </c>
       <c r="E84">
-        <v>-18.71930979747448</v>
+        <v>-17.55362171773803</v>
       </c>
       <c r="F84">
-        <v>-1.439680327393173</v>
+        <v>-2.013106064837491</v>
       </c>
       <c r="G84">
-        <v>-0.9724871450114022</v>
+        <v>-0.5886790479159971</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.705431001978421</v>
       </c>
       <c r="E85">
-        <v>-19.03685092336633</v>
+        <v>-18.26199732133588</v>
       </c>
       <c r="F85">
-        <v>-1.545315395332971</v>
+        <v>-2.212267126022966</v>
       </c>
       <c r="G85">
-        <v>-0.5252291321103255</v>
+        <v>-0.3373920887576177</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.844383852960334</v>
       </c>
       <c r="E86">
-        <v>-20.73307237547141</v>
+        <v>-19.86896707922378</v>
       </c>
       <c r="F86">
-        <v>-1.978452142908777</v>
+        <v>-2.240731486717962</v>
       </c>
       <c r="G86">
-        <v>-0.5838787568840539</v>
+        <v>0.3874948941578192</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.037490872010636</v>
       </c>
       <c r="E87">
-        <v>-21.93046883020956</v>
+        <v>-20.04742065444404</v>
       </c>
       <c r="F87">
-        <v>-2.08241970726674</v>
+        <v>-2.084867532942013</v>
       </c>
       <c r="G87">
-        <v>-0.8174476763162539</v>
+        <v>-0.2607264751591755</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.294409363702445</v>
       </c>
       <c r="E88">
-        <v>-23.20954084215006</v>
+        <v>-22.50643185382313</v>
       </c>
       <c r="F88">
-        <v>-1.906040406393058</v>
+        <v>-2.448982223414355</v>
       </c>
       <c r="G88">
-        <v>-0.6632590178246984</v>
+        <v>-0.1224416774382788</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.618287195720743</v>
       </c>
       <c r="E89">
-        <v>-23.76350453903437</v>
+        <v>-23.46904051668561</v>
       </c>
       <c r="F89">
-        <v>-2.115421864594273</v>
+        <v>-2.966569370970765</v>
       </c>
       <c r="G89">
-        <v>-0.7209585160286559</v>
+        <v>0.1020066890332292</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.014704689545296</v>
       </c>
       <c r="E90">
-        <v>-25.95552596786923</v>
+        <v>-24.50059972478887</v>
       </c>
       <c r="F90">
-        <v>-2.693893187889043</v>
+        <v>-2.409019294801098</v>
       </c>
       <c r="G90">
-        <v>-0.5722620525867513</v>
+        <v>0.1220023840904271</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.489276448356854</v>
       </c>
       <c r="E91">
-        <v>-26.88879917611001</v>
+        <v>-26.75594280567298</v>
       </c>
       <c r="F91">
-        <v>-2.614219154352981</v>
+        <v>-2.970134664272413</v>
       </c>
       <c r="G91">
-        <v>-1.005483352401318</v>
+        <v>-0.1284966652296058</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.039349640045129</v>
       </c>
       <c r="E92">
-        <v>-28.62234883946031</v>
+        <v>-27.58886502990379</v>
       </c>
       <c r="F92">
-        <v>-2.536751891577977</v>
+        <v>-2.881945842202975</v>
       </c>
       <c r="G92">
-        <v>-0.7101528953884748</v>
+        <v>-0.06639745200395684</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.672493059104719</v>
       </c>
       <c r="E93">
-        <v>-30.48124439910592</v>
+        <v>-30.11157600891177</v>
       </c>
       <c r="F93">
-        <v>-2.333924476267712</v>
+        <v>-3.203958759428033</v>
       </c>
       <c r="G93">
-        <v>-1.405019851353801</v>
+        <v>-0.9283343991541424</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.375126881534658</v>
       </c>
       <c r="E94">
-        <v>-32.78866719531525</v>
+        <v>-31.49217414386724</v>
       </c>
       <c r="F94">
-        <v>-2.386782600240348</v>
+        <v>-3.349893073146625</v>
       </c>
       <c r="G94">
-        <v>-1.760744590639568</v>
+        <v>-1.052718216155639</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.147878442930606</v>
       </c>
       <c r="E95">
-        <v>-34.87502347589213</v>
+        <v>-33.75059432283957</v>
       </c>
       <c r="F95">
-        <v>-2.511037710660274</v>
+        <v>-3.7006727051687</v>
       </c>
       <c r="G95">
-        <v>-2.043885618976815</v>
+        <v>-1.428965027239349</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.981966374334071</v>
       </c>
       <c r="E96">
-        <v>-36.68893317474554</v>
+        <v>-36.98133447718381</v>
       </c>
       <c r="F96">
-        <v>-2.850240908228227</v>
+        <v>-3.316386440070787</v>
       </c>
       <c r="G96">
-        <v>-2.440780302588959</v>
+        <v>-2.350008454447682</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.856216230348014</v>
       </c>
       <c r="E97">
-        <v>-39.14570504372784</v>
+        <v>-38.03111852893095</v>
       </c>
       <c r="F97">
-        <v>-2.773737036742679</v>
+        <v>-3.496780009378436</v>
       </c>
       <c r="G97">
-        <v>-3.254283968499607</v>
+        <v>-1.669002752655285</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.778716514360847</v>
       </c>
       <c r="E98">
-        <v>-40.74885050531626</v>
+        <v>-40.57540089387447</v>
       </c>
       <c r="F98">
-        <v>-2.670392404671621</v>
+        <v>-3.604623504814098</v>
       </c>
       <c r="G98">
-        <v>-3.343705114060861</v>
+        <v>-2.743033110324419</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.70123337097619</v>
       </c>
       <c r="E99">
-        <v>-43.88361418154194</v>
+        <v>-43.08306828222896</v>
       </c>
       <c r="F99">
-        <v>-2.691296256081266</v>
+        <v>-3.970736217461992</v>
       </c>
       <c r="G99">
-        <v>-4.035761416863346</v>
+        <v>-3.374569330123486</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.6706285863031</v>
       </c>
       <c r="E100">
-        <v>-45.50973938448228</v>
+        <v>-45.19163219933947</v>
       </c>
       <c r="F100">
-        <v>-2.983198846581964</v>
+        <v>-4.024722577837242</v>
       </c>
       <c r="G100">
-        <v>-4.2984267210402</v>
+        <v>-3.982018020578817</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.58940681308028</v>
       </c>
       <c r="E101">
-        <v>-47.9939787125581</v>
+        <v>-46.19978372529708</v>
       </c>
       <c r="F101">
-        <v>-2.911858189118066</v>
+        <v>-4.220087231215685</v>
       </c>
       <c r="G101">
-        <v>-4.756933967683721</v>
+        <v>-4.636489699873956</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.60077714661102</v>
       </c>
       <c r="E102">
-        <v>-49.82253802482632</v>
+        <v>-49.10744443003809</v>
       </c>
       <c r="F102">
-        <v>-2.954321958920374</v>
+        <v>-4.135120758343137</v>
       </c>
       <c r="G102">
-        <v>-5.660510956626859</v>
+        <v>-4.676441363441881</v>
       </c>
     </row>
   </sheetData>
